--- a/src/v2/api/services/recommender_results.xlsx
+++ b/src/v2/api/services/recommender_results.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="SortedByScore" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SortedByBusinessScore" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RerankParams" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,37 +442,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>contract_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cap_ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
         </is>
       </c>
     </row>
@@ -487,27 +486,27 @@
         <v>1202552</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3</v>
+        <v>0.9441097699259757</v>
       </c>
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.9419631532259521</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -520,27 +519,27 @@
         <v>1156871</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6</v>
+        <v>0.9410667107316282</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cpl</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.9380867643132775</v>
       </c>
     </row>
     <row r="4">
@@ -553,27 +552,27 @@
         <v>1139682</v>
       </c>
       <c r="C4" t="n">
+        <v>0.9176573083881354</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.9182281418827914</v>
       </c>
     </row>
     <row r="5">
@@ -586,27 +585,27 @@
         <v>1159886</v>
       </c>
       <c r="C5" t="n">
+        <v>0.8835644415546507</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cpl</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8808314822607792</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -636,37 +635,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>contract_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cap_ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -682,33 +681,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1156871</v>
+        <v>1202552</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0.9441097699259757</v>
       </c>
       <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cpl</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.9380867643132775</v>
-      </c>
       <c r="J2" t="n">
-        <v>2.176504013824186</v>
+        <v>1.334636591643207</v>
       </c>
     </row>
     <row r="3">
@@ -718,33 +717,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1202552</v>
+        <v>1156871</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0.9410667107316282</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="I3" t="n">
-        <v>0.9419631532259521</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.080262906943883</v>
+        <v>1.329476088377429</v>
       </c>
     </row>
     <row r="4">
@@ -757,30 +756,30 @@
         <v>1139682</v>
       </c>
       <c r="C4" t="n">
+        <v>0.9176573083881354</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.9182281418827914</v>
-      </c>
       <c r="J4" t="n">
-        <v>1.290852904101595</v>
+        <v>1.289889984899181</v>
       </c>
     </row>
     <row r="5">
@@ -793,96 +792,30 @@
         <v>1159886</v>
       </c>
       <c r="C5" t="n">
+        <v>0.8835644415546507</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cpl</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8808314822607792</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.262375999466373</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>gamma</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>rho</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lambda_</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5</v>
+        <v>1.232599289525405</v>
       </c>
     </row>
   </sheetData>
